--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_los_lagos.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>845803</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>774359</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>772760</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>760738</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>760417</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>750000</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>744700</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>741350</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>739990</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>739685</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>738542</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>731032</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>715430</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>712520</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -578,9 +531,6 @@
       <c r="B16">
         <v>705105</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -591,9 +541,6 @@
       <c r="B17">
         <v>700000</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,9 +551,6 @@
       <c r="B18">
         <v>698740</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -617,9 +561,6 @@
       <c r="B19">
         <v>696890</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -630,9 +571,6 @@
       <c r="B20">
         <v>679489</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -643,9 +581,6 @@
       <c r="B21">
         <v>665736.5</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -656,9 +591,6 @@
       <c r="B22">
         <v>652391</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -669,9 +601,6 @@
       <c r="B23">
         <v>630100</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -682,9 +611,6 @@
       <c r="B24">
         <v>623813</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -695,9 +621,6 @@
       <c r="B25">
         <v>618656</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -708,9 +631,6 @@
       <c r="B26">
         <v>602500</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -721,9 +641,6 @@
       <c r="B27">
         <v>600000</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -734,9 +651,6 @@
       <c r="B28">
         <v>600000</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -747,9 +661,6 @@
       <c r="B29">
         <v>600000</v>
       </c>
-      <c r="F29" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -760,9 +671,6 @@
       <c r="B30">
         <v>595854</v>
       </c>
-      <c r="F30" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -772,9 +680,6 @@
       </c>
       <c r="B31">
         <v>562500</v>
-      </c>
-      <c r="F31" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_los_lagos.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>845803</v>
       </c>
+      <c r="C2">
+        <v>743060</v>
+      </c>
+      <c r="D2">
+        <v>102743</v>
+      </c>
+      <c r="E2">
+        <v>13.8270126234759</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>774359</v>
       </c>
+      <c r="C3">
+        <v>674451</v>
+      </c>
+      <c r="D3">
+        <v>99908</v>
+      </c>
+      <c r="E3">
+        <v>14.81323328158755</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>772760</v>
       </c>
+      <c r="C4">
+        <v>685708.5</v>
+      </c>
+      <c r="D4">
+        <v>87051.5</v>
+      </c>
+      <c r="E4">
+        <v>12.69511753172083</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,6 +448,15 @@
       <c r="B5">
         <v>760738</v>
       </c>
+      <c r="C5">
+        <v>631875</v>
+      </c>
+      <c r="D5">
+        <v>128863</v>
+      </c>
+      <c r="E5">
+        <v>20.39374876360041</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -431,6 +467,15 @@
       <c r="B6">
         <v>760417</v>
       </c>
+      <c r="C6">
+        <v>676573</v>
+      </c>
+      <c r="D6">
+        <v>83844</v>
+      </c>
+      <c r="E6">
+        <v>12.39245432495828</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -441,6 +486,15 @@
       <c r="B7">
         <v>750000</v>
       </c>
+      <c r="C7">
+        <v>655539.5</v>
+      </c>
+      <c r="D7">
+        <v>94460.5</v>
+      </c>
+      <c r="E7">
+        <v>14.40958172619651</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -451,6 +505,15 @@
       <c r="B8">
         <v>744700</v>
       </c>
+      <c r="C8">
+        <v>594935</v>
+      </c>
+      <c r="D8">
+        <v>149765</v>
+      </c>
+      <c r="E8">
+        <v>25.17333826384396</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -461,6 +524,15 @@
       <c r="B9">
         <v>741350</v>
       </c>
+      <c r="C9">
+        <v>654060</v>
+      </c>
+      <c r="D9">
+        <v>87290</v>
+      </c>
+      <c r="E9">
+        <v>13.34587040944255</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -471,6 +543,15 @@
       <c r="B10">
         <v>739990</v>
       </c>
+      <c r="C10">
+        <v>623130</v>
+      </c>
+      <c r="D10">
+        <v>116860</v>
+      </c>
+      <c r="E10">
+        <v>18.75371110362203</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -481,6 +562,15 @@
       <c r="B11">
         <v>739685</v>
       </c>
+      <c r="C11">
+        <v>645000</v>
+      </c>
+      <c r="D11">
+        <v>94685</v>
+      </c>
+      <c r="E11">
+        <v>14.67984496124031</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -491,6 +581,15 @@
       <c r="B12">
         <v>738542</v>
       </c>
+      <c r="C12">
+        <v>629880</v>
+      </c>
+      <c r="D12">
+        <v>108662</v>
+      </c>
+      <c r="E12">
+        <v>17.2512224550708</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -501,185 +600,375 @@
       <c r="B13">
         <v>731032</v>
       </c>
+      <c r="C13">
+        <v>626849</v>
+      </c>
+      <c r="D13">
+        <v>104183</v>
+      </c>
+      <c r="E13">
+        <v>16.62011106342995</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B14">
-        <v>715430</v>
+        <v>721532.5</v>
+      </c>
+      <c r="C14">
+        <v>630396</v>
+      </c>
+      <c r="D14">
+        <v>91136.5</v>
+      </c>
+      <c r="E14">
+        <v>14.45702383898375</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Chonchi</t>
+          <t>Curaco de Vélez</t>
         </is>
       </c>
       <c r="B15">
-        <v>712520</v>
+        <v>715430</v>
+      </c>
+      <c r="C15">
+        <v>612190</v>
+      </c>
+      <c r="D15">
+        <v>103240</v>
+      </c>
+      <c r="E15">
+        <v>16.86404547607769</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
+          <t>Chonchi</t>
         </is>
       </c>
       <c r="B16">
-        <v>705105</v>
+        <v>712520</v>
+      </c>
+      <c r="C16">
+        <v>619490</v>
+      </c>
+      <c r="D16">
+        <v>93030</v>
+      </c>
+      <c r="E16">
+        <v>15.01719156080001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Queilén</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="B17">
-        <v>700000</v>
+        <v>705105</v>
+      </c>
+      <c r="C17">
+        <v>601305</v>
+      </c>
+      <c r="D17">
+        <v>103800</v>
+      </c>
+      <c r="E17">
+        <v>17.26245416219723</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
+          <t>Queilén</t>
         </is>
       </c>
       <c r="B18">
-        <v>698740</v>
+        <v>700000</v>
+      </c>
+      <c r="C18">
+        <v>609250</v>
+      </c>
+      <c r="D18">
+        <v>90750</v>
+      </c>
+      <c r="E18">
+        <v>14.89536315141569</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="B19">
-        <v>696890</v>
+        <v>698740</v>
+      </c>
+      <c r="C19">
+        <v>612519</v>
+      </c>
+      <c r="D19">
+        <v>86221</v>
+      </c>
+      <c r="E19">
+        <v>14.0764613016086</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="B20">
-        <v>679489</v>
+        <v>696890</v>
+      </c>
+      <c r="C20">
+        <v>612642</v>
+      </c>
+      <c r="D20">
+        <v>84248</v>
+      </c>
+      <c r="E20">
+        <v>13.75158738708739</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>Dalcahue</t>
         </is>
       </c>
       <c r="B21">
-        <v>665736.5</v>
+        <v>679489</v>
+      </c>
+      <c r="C21">
+        <v>590770</v>
+      </c>
+      <c r="D21">
+        <v>88719</v>
+      </c>
+      <c r="E21">
+        <v>15.01751950843815</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Maullín</t>
+          <t>Ancud</t>
         </is>
       </c>
       <c r="B22">
-        <v>652391</v>
+        <v>665736.5</v>
+      </c>
+      <c r="C22">
+        <v>568271</v>
+      </c>
+      <c r="D22">
+        <v>97465.5</v>
+      </c>
+      <c r="E22">
+        <v>17.15123594200654</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
+          <t>Maullín</t>
         </is>
       </c>
       <c r="B23">
-        <v>630100</v>
+        <v>652391</v>
+      </c>
+      <c r="C23">
+        <v>557128</v>
+      </c>
+      <c r="D23">
+        <v>95263</v>
+      </c>
+      <c r="E23">
+        <v>17.09894315130456</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Puerto Octay</t>
         </is>
       </c>
       <c r="B24">
-        <v>623813</v>
+        <v>630100</v>
+      </c>
+      <c r="C24">
+        <v>550000</v>
+      </c>
+      <c r="D24">
+        <v>80100</v>
+      </c>
+      <c r="E24">
+        <v>14.56363636363636</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="B25">
-        <v>618656</v>
+        <v>623813</v>
+      </c>
+      <c r="C25">
+        <v>546389.5</v>
+      </c>
+      <c r="D25">
+        <v>77423.5</v>
+      </c>
+      <c r="E25">
+        <v>14.17001973866627</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="B26">
-        <v>602500</v>
+        <v>618656</v>
+      </c>
+      <c r="C26">
+        <v>524592</v>
+      </c>
+      <c r="D26">
+        <v>94064</v>
+      </c>
+      <c r="E26">
+        <v>17.93088724189465</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fresia</t>
+          <t>Los Muermos</t>
         </is>
       </c>
       <c r="B27">
-        <v>600000</v>
+        <v>602500</v>
+      </c>
+      <c r="C27">
+        <v>525650</v>
+      </c>
+      <c r="D27">
+        <v>76850</v>
+      </c>
+      <c r="E27">
+        <v>14.61999429278036</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Purranque</t>
+          <t>Fresia</t>
         </is>
       </c>
       <c r="B28">
         <v>600000</v>
       </c>
+      <c r="C28">
+        <v>515638</v>
+      </c>
+      <c r="D28">
+        <v>84362</v>
+      </c>
+      <c r="E28">
+        <v>16.36070266349648</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Río Negro</t>
+          <t>Purranque</t>
         </is>
       </c>
       <c r="B29">
         <v>600000</v>
       </c>
+      <c r="C29">
+        <v>525000</v>
+      </c>
+      <c r="D29">
+        <v>75000</v>
+      </c>
+      <c r="E29">
+        <v>14.28571428571428</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Puyehue</t>
+          <t>Río Negro</t>
         </is>
       </c>
       <c r="B30">
-        <v>595854</v>
+        <v>600000</v>
+      </c>
+      <c r="C30">
+        <v>518956</v>
+      </c>
+      <c r="D30">
+        <v>81044</v>
+      </c>
+      <c r="E30">
+        <v>15.61673822058132</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>595854</v>
+      </c>
+      <c r="C31">
+        <v>505520</v>
+      </c>
+      <c r="D31">
+        <v>90334</v>
+      </c>
+      <c r="E31">
+        <v>17.86952049374901</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>San Juan de la Costa</t>
         </is>
       </c>
-      <c r="B31">
+      <c r="B32">
         <v>562500</v>
+      </c>
+      <c r="C32">
+        <v>500000</v>
+      </c>
+      <c r="D32">
+        <v>62500</v>
+      </c>
+      <c r="E32">
+        <v>12.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_median_a_2022_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_median_a_2022_los_lagos.xlsx
@@ -978,7 +978,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -987,310 +987,215 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ancud</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>665736.5</v>
+          <t>San Pablo</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Calbuco</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>750000</v>
+          <t>Puqueldón</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Castro</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>739685</v>
+          <t>Fresia</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chaitén</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>774359</v>
+          <t>Llanquihue</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chonchi</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>712520</v>
+          <t>Osorno</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cochamó</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>741350</v>
+          <t>Purranque</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>715430</v>
+          <t>Puyehue</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>679489</v>
+          <t>Cochamó</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fresia</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>600000</v>
+          <t>Ancud</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Frutillar</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>623813</v>
+          <t>Quellón</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>698740</v>
+          <t>Queilén</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>760738</v>
+          <t>Chonchi</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>705105</v>
+          <t>Puerto Montt</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>602500</v>
+          <t>Río Negro</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Maullín</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>652391</v>
+          <t>Castro</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Osorno</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>696890</v>
+          <t>Dalcahue</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Palena</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>744700</v>
+          <t>Quemchi</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>760417</v>
+          <t>San Juan de la Costa</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>630100</v>
+          <t>Calbuco</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>845803</v>
+          <t>Chaitén</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>738542</v>
+          <t>Los Muermos</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Purranque</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>600000</v>
+          <t>Maullín</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Puyehue</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>595854</v>
+          <t>Quinchao</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Queilén</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>700000</v>
+          <t>Curaco de Vélez</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Quellón</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>772760</v>
+          <t>Puerto Octay</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quemchi</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>739990</v>
+          <t>Frutillar</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quinchao</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>731032</v>
+          <t>Puerto Varas</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Río Negro</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>600000</v>
+          <t>Hualaihué</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>San Juan de la Costa</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>562500</v>
+          <t>Palena</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>San Pablo</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>618656</v>
+          <t>Futaleufú</t>
+        </is>
       </c>
     </row>
   </sheetData>
